--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY445"/>
+  <dimension ref="A1:AZ445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448601</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448603</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448681</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448692</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448733</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448739</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448720</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448741</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448744</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448571</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448594</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448596</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2419,6 +2499,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448597</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2526,6 +2611,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448608</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2633,6 +2723,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448617</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2740,6 +2835,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448618</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2847,6 +2947,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448620</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2954,6 +3059,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448621</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3061,6 +3171,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448628</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3168,6 +3283,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448629</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3275,6 +3395,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448689</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3382,6 +3507,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448701</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3489,6 +3619,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448712</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3596,6 +3731,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448717</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3703,6 +3843,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448718</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3810,6 +3955,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448719</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448727</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4024,6 +4179,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448732</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4131,6 +4291,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448735</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4238,6 +4403,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448737</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4345,6 +4515,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448738</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4452,6 +4627,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448742</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4559,6 +4739,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448748</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4666,6 +4851,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448751</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4773,6 +4963,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448754</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4880,6 +5075,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448756</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4987,6 +5187,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448634</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5094,6 +5299,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448613</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5201,6 +5411,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448694</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5308,6 +5523,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448725</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5415,6 +5635,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448697</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5522,6 +5747,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448704</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5629,6 +5859,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448708</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5736,6 +5971,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448709</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5843,6 +6083,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448743</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5950,6 +6195,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448593</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6057,6 +6307,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448602</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6164,6 +6419,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448731</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6271,6 +6531,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448734</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6378,6 +6643,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448746</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6485,6 +6755,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448762</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6592,6 +6867,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448590</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6699,6 +6979,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448609</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6806,6 +7091,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448623</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6913,6 +7203,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448632</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7020,6 +7315,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448686</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7127,6 +7427,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448729</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7234,6 +7539,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448750</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7341,6 +7651,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448759</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7463,6 +7778,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448598</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7585,6 +7905,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448740</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7707,6 +8032,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448745</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7819,6 +8149,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448570</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7931,6 +8266,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448698</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8043,6 +8383,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448567</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8155,6 +8500,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448595</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8272,6 +8622,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448696</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8389,6 +8744,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448707</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8506,6 +8866,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448710</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8623,6 +8988,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448711</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8740,6 +9110,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448763</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8852,6 +9227,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448600</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8964,6 +9344,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448722</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9076,6 +9461,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448752</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9183,6 +9573,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448700</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9290,6 +9685,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448591</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9397,6 +9797,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448605</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9504,6 +9909,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448606</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9611,6 +10021,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448625</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9718,6 +10133,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448679</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9825,6 +10245,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448684</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9932,6 +10357,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448728</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10039,6 +10469,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448736</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10146,6 +10581,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448761</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10253,6 +10693,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448611</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10360,6 +10805,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448690</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10467,6 +10917,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448721</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10564,6 +11019,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328007</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10661,6 +11121,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328077</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10758,6 +11223,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328110</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10855,6 +11325,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440059</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10952,6 +11427,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440060</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11049,6 +11529,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440061</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11146,6 +11631,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440062</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11243,6 +11733,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440063</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11340,6 +11835,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440064</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11437,6 +11937,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440065</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11544,6 +12049,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448438</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11651,6 +12161,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448440</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11758,6 +12273,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448444</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11865,6 +12385,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448542</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11972,6 +12497,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448545</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12079,6 +12609,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448564</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12186,6 +12721,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448574</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12293,6 +12833,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448580</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12400,6 +12945,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448769</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12507,6 +13057,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448871</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12614,6 +13169,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448904</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12721,6 +13281,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448912</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12828,6 +13393,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448938</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12935,6 +13505,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448945</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13032,6 +13607,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440099</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13139,6 +13719,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448546</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13236,6 +13821,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440097</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13333,6 +13923,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440098</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13440,6 +14035,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448477</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13547,6 +14147,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448484</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13654,6 +14259,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448487</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13761,6 +14371,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448497</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13868,6 +14483,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448503</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13975,6 +14595,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448515</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14082,6 +14707,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448583</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14189,6 +14819,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448511</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14296,6 +14931,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448812</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14403,6 +15043,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448853</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14500,6 +15145,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328114</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14597,6 +15247,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440093</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14694,6 +15349,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440094</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14791,6 +15451,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440095</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14912,6 +15577,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448925</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15027,6 +15697,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448931</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15142,6 +15817,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448932</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15239,6 +15919,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327988</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15365,6 +16050,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448551</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15487,6 +16177,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448461</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15609,6 +16304,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448896</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15706,6 +16406,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440066</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15813,6 +16518,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448840</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15910,6 +16620,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328033</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16007,6 +16722,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328112</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16104,6 +16824,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440088</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16201,6 +16926,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440089</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16298,6 +17028,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440090</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16395,6 +17130,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440091</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16492,6 +17232,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440092</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16599,6 +17344,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448437</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16706,6 +17456,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448439</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16813,6 +17568,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448442</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16920,6 +17680,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448446</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17027,6 +17792,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448454</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17134,6 +17904,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448455</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17241,6 +18016,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448459</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17348,6 +18128,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448469</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17455,6 +18240,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448470</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17562,6 +18352,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448473</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17669,6 +18464,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448474</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17776,6 +18576,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448476</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17883,6 +18688,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448481</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17990,6 +18800,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448485</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18097,6 +18912,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448489</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18204,6 +19024,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448490</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18311,6 +19136,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448493</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18418,6 +19248,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448495</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18525,6 +19360,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448501</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18632,6 +19472,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448504</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18739,6 +19584,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448505</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18846,6 +19696,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448510</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18953,6 +19808,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448512</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19060,6 +19920,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448513</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19167,6 +20032,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448514</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19274,6 +20144,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448516</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19381,6 +20256,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448518</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19488,6 +20368,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448521</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19595,6 +20480,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448524</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19702,6 +20592,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448526</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19809,6 +20704,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448531</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19916,6 +20816,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448533</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20023,6 +20928,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448540</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20130,6 +21040,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448548</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20237,6 +21152,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448556</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20349,6 +21269,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448560</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20461,6 +21386,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448565</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20568,6 +21498,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448575</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20675,6 +21610,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448578</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20782,6 +21722,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448636</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20889,6 +21834,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448641</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20996,6 +21946,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448645</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21103,6 +22058,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448656</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21210,6 +22170,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448658</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21317,6 +22282,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448661</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21424,6 +22394,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448663</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21531,6 +22506,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448664</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21638,6 +22618,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448666</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21745,6 +22730,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448668</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21852,6 +22842,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448669</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21959,6 +22954,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448673</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22066,6 +23066,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448678</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22173,6 +23178,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448723</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22280,6 +23290,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448764</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22387,6 +23402,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448766</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22494,6 +23514,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448767</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22601,6 +23626,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448768</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22708,6 +23738,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448770</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22815,6 +23850,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448773</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22922,6 +23962,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448777</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23029,6 +24074,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448778</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23136,6 +24186,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448811</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23243,6 +24298,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448813</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23350,6 +24410,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448815</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23457,6 +24522,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448816</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23564,6 +24634,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448817</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23671,6 +24746,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448818</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23778,6 +24858,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448820</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23885,6 +24970,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448822</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23992,6 +25082,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448825</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24099,6 +25194,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448827</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24206,6 +25306,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448829</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24313,6 +25418,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448831</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24420,6 +25530,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448835</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24527,6 +25642,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448837</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24634,6 +25754,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448838</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24741,6 +25866,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448843</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24848,6 +25978,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448849</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24955,6 +26090,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448852</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25062,6 +26202,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448854</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25169,6 +26314,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448855</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25276,6 +26426,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448857</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25383,6 +26538,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448859</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25490,6 +26650,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448862</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25597,6 +26762,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448863</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25704,6 +26874,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448864</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25811,6 +26986,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448868</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25918,6 +27098,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448869</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26025,6 +27210,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448870</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26132,6 +27322,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448875</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26239,6 +27434,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448877</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26346,6 +27546,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448878</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26453,6 +27658,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448882</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26560,6 +27770,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448883</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26667,6 +27882,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448885</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26774,6 +27994,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448887</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26896,6 +28121,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448889</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27003,6 +28233,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448890</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27110,6 +28345,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448894</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27217,6 +28457,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448895</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27324,6 +28569,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448899</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27431,6 +28681,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448901</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27538,6 +28793,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448907</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27645,6 +28905,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448909</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27752,6 +29017,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448910</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27859,6 +29129,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448913</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27966,6 +29241,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448915</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28073,6 +29353,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448916</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28180,6 +29465,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448917</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28287,6 +29577,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448918</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28394,6 +29689,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448920</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28501,6 +29801,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448922</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28608,6 +29913,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448923</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28720,6 +30030,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448929</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28827,6 +30142,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448930</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28934,6 +30254,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448933</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29041,6 +30366,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448934</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29148,6 +30478,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448935</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29255,6 +30590,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448936</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29362,6 +30702,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448937</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29469,6 +30814,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448940</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29576,6 +30926,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448944</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29683,6 +31038,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448946</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29780,6 +31140,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440080</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29877,6 +31242,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440081</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29984,6 +31354,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448488</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30091,6 +31466,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448494</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30198,6 +31578,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448584</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30295,6 +31680,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328084</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30402,6 +31792,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448643</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30499,6 +31894,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327987</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30596,6 +31996,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440086</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30693,6 +32098,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327991</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30790,6 +32200,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328023</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30887,6 +32302,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328027</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30984,6 +32404,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328062</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31081,6 +32506,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328113</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31178,6 +32608,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440049</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31275,6 +32710,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440050</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31372,6 +32812,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440051</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31469,6 +32914,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440052</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31566,6 +33016,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440053</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31663,6 +33118,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440054</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31760,6 +33220,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440055</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31857,6 +33322,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440056</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -31954,6 +33424,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440057</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32061,6 +33536,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448447</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32168,6 +33648,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448456</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32275,6 +33760,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448457</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32382,6 +33872,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448458</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32489,6 +33984,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448520</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32596,6 +34096,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448523</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32703,6 +34208,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448528</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32810,6 +34320,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448530</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32917,6 +34432,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448534</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33024,6 +34544,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448536</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33131,6 +34656,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448549</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33238,6 +34768,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448550</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33345,6 +34880,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448553</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33452,6 +34992,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448563</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33559,6 +35104,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448568</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33666,6 +35216,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448765</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33773,6 +35328,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448772</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33880,6 +35440,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448774</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33987,6 +35552,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448821</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34094,6 +35664,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448828</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34201,6 +35776,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448830</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -34308,6 +35888,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448833</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34415,6 +36000,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448834</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34522,6 +36112,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448839</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34629,6 +36224,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448842</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34736,6 +36336,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448850</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34843,6 +36448,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448860</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34950,6 +36560,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448865</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35057,6 +36672,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448867</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -35164,6 +36784,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448908</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35271,6 +36896,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448911</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -35378,6 +37008,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448941</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35485,6 +37120,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448943</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -35582,6 +37222,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327997</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -35679,6 +37324,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328054</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35776,6 +37426,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440083</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35873,6 +37528,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440084</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35970,6 +37630,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440085</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -36077,6 +37742,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448480</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -36184,6 +37854,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448492</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -36291,6 +37966,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448881</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -36398,6 +38078,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448892</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -36510,6 +38195,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448543</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -36607,6 +38297,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440067</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -36704,6 +38399,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440068</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -36801,6 +38501,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440069</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -36898,6 +38603,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440070</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36995,6 +38705,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440071</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -37102,6 +38817,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448471</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -37209,6 +38929,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448478</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -37316,6 +39041,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448479</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -37423,6 +39153,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448482</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -37530,6 +39265,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448496</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -37637,6 +39377,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448576</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -37749,6 +39494,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448586</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -37856,6 +39606,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448647</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -37963,6 +39718,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448651</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -38070,6 +39830,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448674</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -38177,6 +39942,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448876</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -38284,6 +40054,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448879</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -38391,6 +40166,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448884</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -38513,6 +40293,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448537</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -38635,6 +40420,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448464</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -38757,6 +40547,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448897</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -38864,6 +40659,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448544</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -38971,6 +40771,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448898</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -39078,6 +40883,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448902</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -39200,6 +41010,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448460</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -39307,6 +41122,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448465</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -39429,6 +41249,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448466</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -39551,6 +41376,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448538</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -39661,6 +41491,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440077</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -39771,6 +41606,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440078</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -39883,6 +41723,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448449</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -39995,6 +41840,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448508</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -40107,6 +41957,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448527</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -40219,6 +42074,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448539</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -40331,6 +42191,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448846</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -40443,6 +42308,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448858</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -40545,6 +42415,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328041</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -40655,6 +42530,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440074</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -40772,6 +42652,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448441</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -40884,6 +42769,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448443</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -41001,6 +42891,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448445</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -41118,6 +43013,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448448</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -41235,6 +43135,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448453</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -41352,6 +43257,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448506</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -41469,6 +43379,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448509</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -41586,6 +43501,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448522</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -41698,6 +43618,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448525</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -41815,6 +43740,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448535</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -41932,6 +43862,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448541</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -42044,6 +43979,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448558</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -42161,6 +44101,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448559</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -42273,6 +44218,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448566</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -42390,6 +44340,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448569</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -42507,6 +44462,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448573</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -42619,6 +44579,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448671</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -42736,6 +44701,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448776</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -42848,6 +44818,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448823</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -42960,6 +44935,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448824</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -43077,6 +45057,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448826</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -43194,6 +45179,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448836</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -43306,6 +45296,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448844</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -43423,6 +45418,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448856</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -43540,6 +45540,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448861</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -43657,6 +45662,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448873</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -43774,6 +45784,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448874</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -43891,6 +45906,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448888</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -44008,6 +46028,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448919</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -44113,6 +46138,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440075</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -44218,6 +46248,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440076</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -44330,6 +46365,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448450</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -44442,6 +46482,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448451</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -44554,6 +46599,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448467</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -44666,6 +46716,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448468</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -44778,6 +46833,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448475</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -44890,6 +46950,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448507</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -45002,6 +47067,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448555</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -45114,6 +47184,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448557</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -45226,6 +47301,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448585</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -45338,6 +47418,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448659</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -45450,6 +47535,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448775</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -45562,6 +47652,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448851</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -45674,6 +47769,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448891</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -45786,6 +47886,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448900</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -45898,6 +48003,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448905</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -46010,6 +48120,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448906</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -46107,6 +48222,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328111</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -46219,6 +48339,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448845</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -46331,6 +48456,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448866</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -46443,6 +48573,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448517</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -46550,6 +48685,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448552</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -46647,6 +48787,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328096</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -46744,6 +48889,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440082</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -46851,6 +49001,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448819</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -46958,6 +49113,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448847</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -47055,6 +49215,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328055</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -47162,6 +49327,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448483</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -47269,6 +49439,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448486</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -47376,6 +49551,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448491</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -47483,6 +49663,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448500</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -47590,6 +49775,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448579</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -47697,6 +49887,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448582</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -47804,6 +49999,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448640</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -47911,6 +50111,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448650</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -48018,6 +50223,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448654</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -48125,6 +50335,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448676</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -48222,6 +50437,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440072</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -48329,8 +50549,459 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 6979-2026 artfynd.xlsx
+++ b/artfynd/A 6979-2026 artfynd.xlsx
@@ -16733,7 +16733,7 @@
         <v>131440087</v>
       </c>
       <c r="B145" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
